--- a/data/trans_dic/P56$auxiliar-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$auxiliar-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,96; 61,26</t>
+          <t>9,98; 70,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 39,69</t>
+          <t>5,12; 40,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,56; 54,45</t>
+          <t>23,23; 53,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 32,91</t>
+          <t>9,49; 33,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 23,47</t>
+          <t>2,81; 21,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,04; 43,49</t>
+          <t>27,22; 42,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,42; 32,87</t>
+          <t>11,49; 35,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 23,45</t>
+          <t>5,24; 21,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,06; 42,83</t>
+          <t>29,25; 42,7</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 29,02</t>
+          <t>3,4; 28,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,38; 40,99</t>
+          <t>13,72; 40,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,53</t>
+          <t>0,0; 21,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,24; 31,47</t>
+          <t>10,8; 30,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 22,47</t>
+          <t>2,96; 25,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,73; 37,87</t>
+          <t>22,9; 38,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,75</t>
+          <t>0,0; 15,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,22; 26,91</t>
+          <t>10,69; 27,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 16,63</t>
+          <t>2,01; 18,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,49; 36,7</t>
+          <t>22,46; 36,18</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,72</t>
+          <t>0,0; 21,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 35,59</t>
+          <t>5,78; 37,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,53</t>
+          <t>0,0; 32,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 33,98</t>
+          <t>9,3; 35,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,59</t>
+          <t>0,0; 27,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,03; 33,41</t>
+          <t>13,96; 33,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,16</t>
+          <t>0,0; 22,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 25,92</t>
+          <t>7,56; 29,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 19,59</t>
+          <t>1,55; 19,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,12; 28,93</t>
+          <t>13,53; 29,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,37</t>
+          <t>0,0; 25,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 20,08</t>
+          <t>3,35; 20,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 28,18</t>
+          <t>3,64; 30,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,06; 31,5</t>
+          <t>10,18; 32,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,68</t>
+          <t>0,0; 12,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,13; 29,91</t>
+          <t>15,84; 29,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 21,77</t>
+          <t>2,56; 22,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 25,76</t>
+          <t>8,44; 25,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,17</t>
+          <t>0,0; 9,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,54; 24,43</t>
+          <t>13,74; 24,96</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 20,49</t>
+          <t>5,47; 20,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 13,61</t>
+          <t>2,24; 13,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,82; 28,69</t>
+          <t>15,63; 29,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 13,79</t>
+          <t>2,34; 13,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,74; 26,28</t>
+          <t>14,2; 26,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,62</t>
+          <t>3,08; 11,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,79; 31,52</t>
+          <t>23,68; 31,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,99</t>
+          <t>1,64; 10,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,32; 22,17</t>
+          <t>13,26; 21,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,07</t>
+          <t>3,68; 10,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,5; 29,15</t>
+          <t>22,57; 29,6</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1650</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1054; 6486</t>
+          <t>1056; 7435</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>837; 7530</t>
+          <t>971; 7593</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6164; 13664</t>
+          <t>5829; 13409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4261; 15174</t>
+          <t>4377; 15670</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1131; 9347</t>
+          <t>1120; 8396</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17342; 26899</t>
+          <t>16833; 26571</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1873</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6478; 18636</t>
+          <t>6517; 19893</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3010; 13786</t>
+          <t>3081; 12820</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25269; 37239</t>
+          <t>25426; 37124</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1771</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1095; 9402</t>
+          <t>1103; 9219</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1612</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3513; 10013</t>
+          <t>3350; 9839</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5345</t>
+          <t>0; 5991</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7381; 20665</t>
+          <t>7092; 20192</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1197; 9226</t>
+          <t>1216; 10319</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15210; 25338</t>
+          <t>15320; 25512</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5398</t>
+          <t>0; 6484</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10999; 26391</t>
+          <t>10484; 26617</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1179; 10071</t>
+          <t>1216; 11061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20539; 33523</t>
+          <t>20512; 33043</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1443</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2192</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4171</t>
+          <t>0; 3776</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>753; 7225</t>
+          <t>1172; 7642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4682</t>
+          <t>0; 5691</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4120; 14337</t>
+          <t>3926; 14981</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 8968</t>
+          <t>0; 9796</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5924; 14106</t>
+          <t>5892; 13961</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5696</t>
+          <t>0; 5533</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4125; 14558</t>
+          <t>4245; 16331</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>832; 10310</t>
+          <t>816; 10497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8203; 18088</t>
+          <t>8462; 18506</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1479</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5681</t>
+          <t>0; 5521</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1690</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1029; 6473</t>
+          <t>1080; 6561</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1169; 9056</t>
+          <t>1171; 9776</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5159; 16151</t>
+          <t>5217; 16642</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6522</t>
+          <t>0; 6892</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12912; 23945</t>
+          <t>12680; 23510</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1173; 9884</t>
+          <t>1163; 10017</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5994; 18755</t>
+          <t>6146; 18638</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 6592</t>
+          <t>0; 6625</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15201; 27436</t>
+          <t>15426; 28029</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4144; 16088</t>
+          <t>4292; 16169</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1641; 9814</t>
+          <t>1616; 9403</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16150; 29283</t>
+          <t>15949; 29888</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2942; 12902</t>
+          <t>2188; 12254</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30252; 53940</t>
+          <t>29141; 53902</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6053; 21681</t>
+          <t>5291; 20263</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59722; 79133</t>
+          <t>59452; 79282</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2256; 12751</t>
+          <t>2331; 14510</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37799; 62918</t>
+          <t>37622; 61995</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8909; 24568</t>
+          <t>8984; 25963</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>79430; 102926</t>
+          <t>79688; 104508</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$auxiliar-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$auxiliar-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 70,22</t>
+          <t>9,95; 67,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 40,02</t>
+          <t>4,54; 40,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,23; 53,43</t>
+          <t>25,87; 55,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,49; 33,98</t>
+          <t>7,49; 33,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 21,08</t>
+          <t>2,85; 23,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,22; 42,96</t>
+          <t>27,88; 43,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,49; 35,08</t>
+          <t>11,3; 34,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 21,81</t>
+          <t>4,83; 22,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,25; 42,7</t>
+          <t>28,98; 42,95</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 28,46</t>
+          <t>3,57; 30,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,72; 40,28</t>
+          <t>15,18; 41,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,89</t>
+          <t>0,0; 19,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,8; 30,75</t>
+          <t>11,55; 31,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 25,13</t>
+          <t>2,91; 23,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,9; 38,13</t>
+          <t>21,36; 36,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,31</t>
+          <t>0,0; 13,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,69; 27,14</t>
+          <t>11,3; 26,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 18,26</t>
+          <t>1,97; 16,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,46; 36,18</t>
+          <t>22,22; 35,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,48</t>
+          <t>0,0; 23,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 37,65</t>
+          <t>3,92; 36,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,25</t>
+          <t>0,0; 25,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,3; 35,5</t>
+          <t>9,98; 35,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,95</t>
+          <t>0,0; 28,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 33,06</t>
+          <t>13,15; 32,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,49</t>
+          <t>0,0; 21,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 29,07</t>
+          <t>7,57; 26,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 19,95</t>
+          <t>1,53; 18,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,53; 29,6</t>
+          <t>12,88; 28,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,62</t>
+          <t>0,0; 27,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 20,35</t>
+          <t>3,35; 20,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 30,42</t>
+          <t>3,47; 27,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,18; 32,46</t>
+          <t>10,0; 32,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,34</t>
+          <t>0,0; 10,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,84; 29,37</t>
+          <t>16,17; 30,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 22,06</t>
+          <t>2,55; 23,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 25,6</t>
+          <t>8,57; 26,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,21</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,74; 24,96</t>
+          <t>13,98; 25,46</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -1282,57 +1282,57 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 20,6</t>
+          <t>4,85; 20,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 13,04</t>
+          <t>2,18; 13,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,63; 29,28</t>
+          <t>15,47; 28,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 13,1</t>
+          <t>2,41; 13,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,2; 26,26</t>
+          <t>14,51; 25,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 11,8</t>
+          <t>3,06; 12,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,68; 31,58</t>
+          <t>24,08; 31,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 10,23</t>
+          <t>1,62; 9,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,26; 21,85</t>
+          <t>13,3; 23,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,65</t>
+          <t>3,67; 10,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,57; 29,6</t>
+          <t>22,61; 29,23</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>22810</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31035</t>
+          <t>32807</t>
         </is>
       </c>
     </row>
@@ -1650,17 +1650,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1056; 7435</t>
+          <t>1053; 7187</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>971; 7593</t>
+          <t>861; 7680</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5829; 13409</t>
+          <t>6750; 14433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4377; 15670</t>
+          <t>3456; 15445</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1120; 8396</t>
+          <t>1133; 9304</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16833; 26571</t>
+          <t>18347; 28634</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1690,17 +1690,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6517; 19893</t>
+          <t>6405; 19645</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3081; 12820</t>
+          <t>2839; 13133</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25426; 37124</t>
+          <t>26629; 39470</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>21807</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26527</t>
+          <t>28686</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1103; 9219</t>
+          <t>1156; 10000</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1868,47 +1868,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3350; 9839</t>
+          <t>3984; 10927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5991</t>
+          <t>0; 5226</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7092; 20192</t>
+          <t>7586; 20778</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1216; 10319</t>
+          <t>1194; 9684</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15320; 25512</t>
+          <t>15813; 27388</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6484</t>
+          <t>0; 5563</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10484; 26617</t>
+          <t>11079; 26267</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1216; 11061</t>
+          <t>1195; 10117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20512; 33043</t>
+          <t>22289; 35513</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>14174</t>
         </is>
       </c>
     </row>
@@ -2071,52 +2071,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3776</t>
+          <t>0; 4161</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1172; 7642</t>
+          <t>907; 8354</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5691</t>
+          <t>0; 4539</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3926; 14981</t>
+          <t>4210; 14888</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 9796</t>
+          <t>0; 9875</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5892; 13961</t>
+          <t>6269; 15595</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5533</t>
+          <t>0; 5333</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4245; 16331</t>
+          <t>4252; 15043</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>816; 10497</t>
+          <t>803; 9832</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8462; 18506</t>
+          <t>9121; 20465</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20910</t>
+          <t>23109</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5521</t>
+          <t>0; 6014</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2284,47 +2284,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1080; 6561</t>
+          <t>1111; 6649</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1171; 9776</t>
+          <t>1115; 8978</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5217; 16642</t>
+          <t>5125; 16810</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6892</t>
+          <t>0; 5878</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12680; 23510</t>
+          <t>14215; 26465</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1163; 10017</t>
+          <t>1158; 10854</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6146; 18638</t>
+          <t>6239; 19006</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 6625</t>
+          <t>0; 6752</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15426; 28029</t>
+          <t>16913; 30814</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68974</t>
+          <t>75295</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>98775</t>
         </is>
       </c>
     </row>
@@ -2482,57 +2482,57 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4292; 16169</t>
+          <t>3809; 15906</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1616; 9403</t>
+          <t>1575; 9401</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15949; 29888</t>
+          <t>16799; 31442</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2188; 12254</t>
+          <t>2251; 12977</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29141; 53902</t>
+          <t>29788; 52982</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5291; 20263</t>
+          <t>5260; 20992</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59452; 79282</t>
+          <t>66317; 86929</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2331; 14510</t>
+          <t>2297; 13806</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37622; 61995</t>
+          <t>37746; 65453</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8984; 25963</t>
+          <t>8941; 25086</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>79688; 104508</t>
+          <t>86824; 112260</t>
         </is>
       </c>
     </row>
